--- a/STEP1_REVISED/Step5A_Holdout_Audit_CrossResponse.xlsx
+++ b/STEP1_REVISED/Step5A_Holdout_Audit_CrossResponse.xlsx
@@ -500,28 +500,28 @@
         <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>94.11764705882354</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>5.88235294117647</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9992412761360363</v>
+        <v>0.9949181447997554</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008159307440261979</v>
+        <v>0.01642524095020904</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006184869419067564</v>
+        <v>0.01357906231616343</v>
       </c>
       <c r="K2" t="n">
-        <v>1.45683601761296</v>
+        <v>2.769118171975693</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -556,16 +556,16 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9889304507702699</v>
+        <v>0.9872736893509028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0995469829666622</v>
+        <v>0.1157454401324335</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07209730070704991</v>
+        <v>0.08651182752368014</v>
       </c>
       <c r="K3" t="n">
-        <v>4.497070053622965</v>
+        <v>3.788920540897504</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -594,22 +594,22 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.88235294117647</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9877437129855192</v>
+        <v>0.9883245581405847</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01173831593491012</v>
+        <v>0.0106026319035138</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008760980583228333</v>
+        <v>0.008185474354219711</v>
       </c>
       <c r="K4" t="n">
-        <v>3.93134048941068</v>
+        <v>8.463444490555306</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -695,31 +695,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>0.023333333</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+        <v>0.846666667</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8525565339359761</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.00588986693597604</v>
+      </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INVALID_NONFINITE</t>
+          <t>VALID</t>
         </is>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.00588986693597604</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -728,22 +734,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E3" t="n">
-        <v>0.916666667</v>
+        <v>0.903333333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9208243153885171</v>
+        <v>0.8941871233014876</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004157648388517066</v>
+        <v>-0.00914620969851232</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -757,7 +763,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004157648388517066</v>
+        <v>0.00914620969851232</v>
       </c>
     </row>
     <row r="4">
@@ -767,37 +773,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9866666670000001</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9812548695006634</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.005411797499336624</v>
-      </c>
+        <v>0.993333333</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>INVALID_NONFINITE</t>
         </is>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.005411797499336624</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -806,22 +806,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>0.606666667</v>
+        <v>0.413333333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5845854986851003</v>
+        <v>0.3852428307822398</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0220811683148997</v>
+        <v>-0.02809050221776022</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -835,7 +835,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0220811683148997</v>
+        <v>0.02809050221776022</v>
       </c>
     </row>
     <row r="6">
@@ -845,22 +845,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>0.873333333</v>
+        <v>0.706666667</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8647175506220238</v>
+        <v>0.6904483212093069</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.008615782377976222</v>
+        <v>-0.01621834579069314</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -874,7 +874,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008615782377976222</v>
+        <v>0.01621834579069314</v>
       </c>
     </row>
     <row r="7">
@@ -884,22 +884,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9866666670000001</v>
+        <v>0.766666667</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9844910926508779</v>
+        <v>0.7323201424258879</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.002175574349122189</v>
+        <v>-0.03434652457411203</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -913,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002175574349122189</v>
+        <v>0.03434652457411203</v>
       </c>
     </row>
     <row r="8">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>0.043333333</v>
+        <v>0.306666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0394019570750633</v>
+        <v>0.2918065384581127</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.003931375924936698</v>
+        <v>-0.01486012854188729</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -952,7 +952,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003931375924936698</v>
+        <v>0.01486012854188729</v>
       </c>
     </row>
     <row r="9">
@@ -962,22 +962,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>0.86</v>
+        <v>0.796666667</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8646702590253853</v>
+        <v>0.8095848206326297</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004670259025385315</v>
+        <v>0.01291815363262971</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -991,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004670259025385315</v>
+        <v>0.01291815363262971</v>
       </c>
     </row>
     <row r="10">
@@ -1013,10 +1013,10 @@
         <v>0.91</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9232311235112848</v>
+        <v>0.9209415779463459</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01323112351128475</v>
+        <v>0.01094157794634587</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -1030,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01323112351128475</v>
+        <v>0.01094157794634587</v>
       </c>
     </row>
     <row r="11">
@@ -1040,22 +1040,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>0.046666667</v>
+        <v>0.24</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04692389301361734</v>
+        <v>0.2133003104049293</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0002572260136173357</v>
+        <v>-0.02669968959507069</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -1069,7 +1069,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002572260136173357</v>
+        <v>0.02669968959507069</v>
       </c>
     </row>
     <row r="12">
@@ -1079,22 +1079,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E12" t="n">
-        <v>0.786666667</v>
+        <v>0.826666667</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7897072389569375</v>
+        <v>0.8221933065868315</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003040571956937521</v>
+        <v>-0.004473360413168481</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -1108,7 +1108,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0.003040571956937521</v>
+        <v>0.004473360413168481</v>
       </c>
     </row>
     <row r="13">
@@ -1118,22 +1118,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>0.956666667</v>
+        <v>0.643333333</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9590703201198684</v>
+        <v>0.6481067739882954</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002403653119868343</v>
+        <v>0.004773440988295463</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002403653119868343</v>
+        <v>0.004773440988295463</v>
       </c>
     </row>
     <row r="14">
@@ -1157,22 +1157,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E14" t="n">
-        <v>0.496666667</v>
+        <v>0.83</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5067848662662509</v>
+        <v>0.8290928268921984</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01011819926625085</v>
+        <v>-0.0009071731078015288</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -1186,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01011819926625085</v>
+        <v>0.0009071731078015288</v>
       </c>
     </row>
     <row r="15">
@@ -1196,22 +1196,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E15" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7897162855129773</v>
+        <v>0.8577962504781058</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0002837144870226904</v>
+        <v>0.007796250478105837</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1225,7 +1225,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0002837144870226904</v>
+        <v>0.007796250478105837</v>
       </c>
     </row>
     <row r="16">
@@ -1235,22 +1235,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="E16" t="n">
-        <v>0.903333333</v>
+        <v>0.316666667</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9073534727821729</v>
+        <v>0.3063171783067324</v>
       </c>
       <c r="G16" t="n">
-        <v>0.004020139782172971</v>
+        <v>-0.01034948869326763</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0.004020139782172971</v>
+        <v>0.01034948869326763</v>
       </c>
     </row>
     <row r="17">
@@ -1274,22 +1274,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="E17" t="n">
-        <v>0.45</v>
+        <v>0.863333333</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4425755471119286</v>
+        <v>0.8796085551288252</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.00742445288807142</v>
+        <v>0.01627522212882515</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1303,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00742445288807142</v>
+        <v>0.01627522212882515</v>
       </c>
     </row>
     <row r="18">
@@ -1313,37 +1313,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.6971352237996813</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.007135223799681345</v>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>INVALID_NONFINITE</t>
         </is>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.007135223799681345</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1352,22 +1346,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>1.44921875</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7522880136377822</v>
+        <v>1.528794962695607</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2477119863622178</v>
+        <v>0.079576212695607</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1378,10 +1372,10 @@
         </is>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2477119863622178</v>
+        <v>0.079576212695607</v>
       </c>
     </row>
     <row r="20">
@@ -1391,22 +1385,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E20" t="n">
-        <v>1.52203125</v>
+        <v>1.50375</v>
       </c>
       <c r="F20" t="n">
-        <v>1.506520340015134</v>
+        <v>1.526633566736228</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.01551090998486626</v>
+        <v>0.02288356673622793</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1420,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01551090998486626</v>
+        <v>0.02288356673622793</v>
       </c>
     </row>
     <row r="21">
@@ -1430,22 +1424,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" t="n">
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E21" t="n">
-        <v>1.589375</v>
+        <v>1.60703125</v>
       </c>
       <c r="F21" t="n">
-        <v>1.623738401828795</v>
+        <v>1.822758838958556</v>
       </c>
       <c r="G21" t="n">
-        <v>0.03436340182879527</v>
+        <v>0.2157275889585559</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1456,10 +1450,10 @@
         </is>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.03436340182879527</v>
+        <v>0.2157275889585559</v>
       </c>
     </row>
     <row r="22">
@@ -1469,22 +1463,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" t="n">
         <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E22" t="n">
-        <v>1.682526433</v>
+        <v>1.385364496</v>
       </c>
       <c r="F22" t="n">
-        <v>1.597239222674139</v>
+        <v>1.334476038656485</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.08528721032586128</v>
+        <v>-0.0508884573435151</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1498,7 +1492,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08528721032586128</v>
+        <v>0.0508884573435151</v>
       </c>
     </row>
     <row r="23">
@@ -1508,22 +1502,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C23" t="n">
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>2.098219254</v>
+        <v>1.850862549</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0528932527158</v>
+        <v>1.777380462962752</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.04532600128419961</v>
+        <v>-0.0734820860372476</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1537,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0.04532600128419961</v>
+        <v>0.0734820860372476</v>
       </c>
     </row>
     <row r="24">
@@ -1547,22 +1541,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C24" t="n">
         <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="E24" t="n">
-        <v>2.228992766</v>
+        <v>1.926265999</v>
       </c>
       <c r="F24" t="n">
-        <v>2.231275328801412</v>
+        <v>1.902655813269863</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00228256280141137</v>
+        <v>-0.0236101857301374</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1576,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00228256280141137</v>
+        <v>0.0236101857301374</v>
       </c>
     </row>
     <row r="25">
@@ -1586,22 +1580,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C25" t="n">
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>1.461111111</v>
       </c>
       <c r="F25" t="n">
-        <v>1.09565123432941</v>
+        <v>1.495270051567742</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09565123432941025</v>
+        <v>0.03415894056774182</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1615,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0.09565123432941025</v>
+        <v>0.03415894056774182</v>
       </c>
     </row>
     <row r="26">
@@ -1625,22 +1619,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C26" t="n">
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E26" t="n">
-        <v>2.479059829</v>
+        <v>2.400854701</v>
       </c>
       <c r="F26" t="n">
-        <v>2.559402180650787</v>
+        <v>2.483531642048405</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08034235165078663</v>
+        <v>0.08267694104840473</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1654,7 +1648,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.08034235165078663</v>
+        <v>0.08267694104840473</v>
       </c>
     </row>
     <row r="27">
@@ -1676,10 +1670,10 @@
         <v>2.526495726</v>
       </c>
       <c r="F27" t="n">
-        <v>2.575503813402324</v>
+        <v>2.57911609134373</v>
       </c>
       <c r="G27" t="n">
-        <v>0.04900808740232421</v>
+        <v>0.05262036534373049</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1693,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0.04900808740232421</v>
+        <v>0.05262036534373049</v>
       </c>
     </row>
     <row r="28">
@@ -1703,22 +1697,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C28" t="n">
         <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>1.710181137</v>
       </c>
       <c r="F28" t="n">
-        <v>1.12689881925892</v>
+        <v>1.610618651536808</v>
       </c>
       <c r="G28" t="n">
-        <v>0.12689881925892</v>
+        <v>-0.09956248546319157</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1732,7 +1726,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0.12689881925892</v>
+        <v>0.09956248546319157</v>
       </c>
     </row>
     <row r="29">
@@ -1742,22 +1736,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" t="n">
         <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E29" t="n">
-        <v>3.026858214</v>
+        <v>3.090568395</v>
       </c>
       <c r="F29" t="n">
-        <v>3.009460045070795</v>
+        <v>3.072045986687107</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.01739816892920487</v>
+        <v>-0.0185224083128932</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1771,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01739816892920487</v>
+        <v>0.0185224083128932</v>
       </c>
     </row>
     <row r="30">
@@ -1781,22 +1775,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D30" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="E30" t="n">
-        <v>3.286071205</v>
+        <v>3.179091688</v>
       </c>
       <c r="F30" t="n">
-        <v>3.24567248275369</v>
+        <v>3.204690415163836</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.04039872224631003</v>
+        <v>0.02559872716383627</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1810,7 +1804,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0.04039872224631003</v>
+        <v>0.02559872716383627</v>
       </c>
     </row>
     <row r="31">
@@ -1820,22 +1814,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C31" t="n">
         <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E31" t="n">
-        <v>2.65638389</v>
+        <v>3.600685518</v>
       </c>
       <c r="F31" t="n">
-        <v>2.622679896518527</v>
+        <v>3.658969439985555</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.03370399348147313</v>
+        <v>0.05828392198555532</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1849,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0.03370399348147313</v>
+        <v>0.05828392198555532</v>
       </c>
     </row>
     <row r="32">
@@ -1859,22 +1853,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C32" t="n">
         <v>14</v>
       </c>
       <c r="D32" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E32" t="n">
-        <v>3.525278492</v>
+        <v>3.618680377</v>
       </c>
       <c r="F32" t="n">
-        <v>3.579706385985428</v>
+        <v>3.695405003198265</v>
       </c>
       <c r="G32" t="n">
-        <v>0.05442789398542835</v>
+        <v>0.07672462619826481</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1888,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0.05442789398542835</v>
+        <v>0.07672462619826481</v>
       </c>
     </row>
     <row r="33">
@@ -1898,22 +1892,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="E33" t="n">
-        <v>3.77377892</v>
+        <v>2.622767857</v>
       </c>
       <c r="F33" t="n">
-        <v>3.774031596595468</v>
+        <v>2.365304014835883</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0002526765954682375</v>
+        <v>-0.2574638421641171</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1927,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0002526765954682375</v>
+        <v>0.2574638421641171</v>
       </c>
     </row>
     <row r="34">
@@ -1937,22 +1931,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
         <v>16</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="E34" t="n">
-        <v>3.094866071</v>
+        <v>4.3046875</v>
       </c>
       <c r="F34" t="n">
-        <v>2.868624763228428</v>
+        <v>4.344883005500296</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2262413077715721</v>
+        <v>0.0401955055002956</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1966,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2262413077715721</v>
+        <v>0.0401955055002956</v>
       </c>
     </row>
     <row r="35">
@@ -1976,22 +1970,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C35" t="n">
         <v>16</v>
       </c>
       <c r="D35" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E35" t="n">
-        <v>3.943080357</v>
+        <v>4.681919643</v>
       </c>
       <c r="F35" t="n">
-        <v>4.013929140781599</v>
+        <v>4.423194436346759</v>
       </c>
       <c r="G35" t="n">
-        <v>0.07084878378159898</v>
+        <v>-0.2587252066532404</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -2002,10 +1996,10 @@
         </is>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.07084878378159898</v>
+        <v>0.2587252066532404</v>
       </c>
     </row>
     <row r="36">
@@ -2015,36 +2009,36 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C36" t="n">
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.129812368</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.03329454901508362</v>
+        <v>0.1394920783556689</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.03329454901508362</v>
+        <v>0.009679710355668919</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PHYSICAL_VIOLATION</t>
+          <t>VALID</t>
         </is>
       </c>
       <c r="J36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.03329454901508362</v>
+        <v>0.009679710355668919</v>
       </c>
     </row>
     <row r="37">
@@ -2054,22 +2048,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C37" t="n">
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E37" t="n">
-        <v>0.155513347</v>
+        <v>0.149682126</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1667982785125635</v>
+        <v>0.1604931609355467</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01128493151256346</v>
+        <v>0.01081103493554669</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -2083,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01128493151256346</v>
+        <v>0.01081103493554669</v>
       </c>
     </row>
     <row r="38">
@@ -2093,22 +2087,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" t="n">
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E38" t="n">
-        <v>0.180976271</v>
+        <v>0.185595806</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1759598333787052</v>
+        <v>0.1846307322571314</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.00501643762129475</v>
+        <v>-0.0009650737428685552</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -2119,10 +2113,10 @@
         </is>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.00501643762129475</v>
+        <v>0.0009650737428685552</v>
       </c>
     </row>
     <row r="39">
@@ -2132,22 +2126,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" t="n">
         <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E39" t="n">
-        <v>0.12191595</v>
+        <v>0.056957217</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1027490811059167</v>
+        <v>0.0628784146130543</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.01916686889408334</v>
+        <v>0.005921197613054298</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -2161,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0.01916686889408334</v>
+        <v>0.005921197613054298</v>
       </c>
     </row>
     <row r="40">
@@ -2171,22 +2165,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C40" t="n">
         <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>0.226452432</v>
+        <v>0.160936952</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2197664400116286</v>
+        <v>0.1407397283889588</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.006685991988371415</v>
+        <v>-0.02019722361104118</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2200,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.006685991988371415</v>
+        <v>0.02019722361104118</v>
       </c>
     </row>
     <row r="41">
@@ -2210,22 +2204,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C41" t="n">
         <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>0.269507547</v>
+        <v>0.182634575</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2579142148047501</v>
+        <v>0.1683021023044128</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.01159333219524988</v>
+        <v>-0.01433247269558716</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2239,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.01159333219524988</v>
+        <v>0.01433247269558716</v>
       </c>
     </row>
     <row r="42">
@@ -2249,22 +2243,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C42" t="n">
         <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>0.047106137</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01005288010443478</v>
+        <v>0.07148426095306321</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01005288010443478</v>
+        <v>0.02437812395306321</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2278,7 +2272,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01005288010443478</v>
+        <v>0.02437812395306321</v>
       </c>
     </row>
     <row r="43">
@@ -2288,22 +2282,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
         <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E43" t="n">
-        <v>0.249815332</v>
+        <v>0.226319718</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2605642008276675</v>
+        <v>0.232013548761956</v>
       </c>
       <c r="G43" t="n">
-        <v>0.01074886882766751</v>
+        <v>0.005693830761955981</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2317,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0.01074886882766751</v>
+        <v>0.005693830761955981</v>
       </c>
     </row>
     <row r="44">
@@ -2339,10 +2333,10 @@
         <v>0.267696194</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2779189680215666</v>
+        <v>0.2774301832161995</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01022277402156663</v>
+        <v>0.009733989216199501</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2356,7 +2350,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0.01022277402156663</v>
+        <v>0.009733989216199501</v>
       </c>
     </row>
     <row r="45">
@@ -2366,22 +2360,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C45" t="n">
         <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>0.049264635</v>
       </c>
       <c r="F45" t="n">
-        <v>0.001291001190873959</v>
+        <v>0.06449612401287035</v>
       </c>
       <c r="G45" t="n">
-        <v>0.001291001190873959</v>
+        <v>0.01523148901287034</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2395,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0.001291001190873959</v>
+        <v>0.01523148901287034</v>
       </c>
     </row>
     <row r="46">
@@ -2405,22 +2399,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C46" t="n">
         <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E46" t="n">
-        <v>0.260389238</v>
+        <v>0.276412389</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2592092589792414</v>
+        <v>0.2730758271227815</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.00117997902075867</v>
+        <v>-0.00333656187721848</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2434,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0.00117997902075867</v>
+        <v>0.00333656187721848</v>
       </c>
     </row>
     <row r="47">
@@ -2444,22 +2438,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C47" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="E47" t="n">
-        <v>0.328983913</v>
+        <v>0.219689143</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3305368444637373</v>
+        <v>0.216838186207731</v>
       </c>
       <c r="G47" t="n">
-        <v>0.001552931463737306</v>
+        <v>-0.002850956792269044</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2473,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0.001552931463737306</v>
+        <v>0.002850956792269044</v>
       </c>
     </row>
     <row r="48">
@@ -2483,22 +2477,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C48" t="n">
         <v>14</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E48" t="n">
-        <v>0.154289085</v>
+        <v>0.298662612</v>
       </c>
       <c r="F48" t="n">
-        <v>0.148986179549073</v>
+        <v>0.2930033917528271</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.005302905450926959</v>
+        <v>-0.005659220247172858</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2512,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0.005302905450926959</v>
+        <v>0.005659220247172858</v>
       </c>
     </row>
     <row r="49">
@@ -2522,22 +2516,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C49" t="n">
         <v>14</v>
       </c>
       <c r="D49" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E49" t="n">
-        <v>0.281931145</v>
+        <v>0.306444136</v>
       </c>
       <c r="F49" t="n">
-        <v>0.278722065458306</v>
+        <v>0.3059109772332567</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.003209079541694027</v>
+        <v>-0.000533158766743258</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2551,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>0.003209079541694027</v>
+        <v>0.000533158766743258</v>
       </c>
     </row>
     <row r="50">
@@ -2561,22 +2555,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D50" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="E50" t="n">
-        <v>0.330783285</v>
+        <v>0.09732608700000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.332123367912947</v>
+        <v>0.09967786540793341</v>
       </c>
       <c r="G50" t="n">
-        <v>0.001340082912947016</v>
+        <v>0.002351778407933408</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2590,7 +2584,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>0.001340082912947016</v>
+        <v>0.002351778407933408</v>
       </c>
     </row>
     <row r="51">
@@ -2600,22 +2594,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C51" t="n">
         <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="E51" t="n">
-        <v>0.151308161</v>
+        <v>0.329237345</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1462528550564679</v>
+        <v>0.3304624708811604</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.005055305943532068</v>
+        <v>0.001225125881160416</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2629,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0.005055305943532068</v>
+        <v>0.001225125881160416</v>
       </c>
     </row>
     <row r="52">
@@ -2639,22 +2633,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C52" t="n">
         <v>16</v>
       </c>
       <c r="D52" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E52" t="n">
-        <v>0.255832691</v>
+        <v>0.367215621</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2677714412100963</v>
+        <v>0.3609635048486182</v>
       </c>
       <c r="G52" t="n">
-        <v>0.01193875021009627</v>
+        <v>-0.00625211615138177</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2665,10 +2659,10 @@
         </is>
       </c>
       <c r="J52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.01193875021009627</v>
+        <v>0.00625211615138177</v>
       </c>
     </row>
   </sheetData>
@@ -2749,16 +2743,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="E2" t="n">
-        <v>0.023333333</v>
+        <v>0.993333333</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -2778,41 +2772,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vch</t>
+          <t>hc_hi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
+        <v>260</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.03329454901508362</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.03329454901508362</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PHYSICAL_VIOLATION</t>
+          <t>INVALID_NONFINITE</t>
         </is>
       </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0.03329454901508362</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2877,13 +2865,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2891,10 +2879,14 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.023333333</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>0.846666667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8416666665</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8525565339359761</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2903,13 +2895,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2917,13 +2909,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.916666667</v>
+        <v>0.903333333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.918333333</v>
+        <v>0.8933333335</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9208243153885171</v>
+        <v>0.8941871233014876</v>
       </c>
     </row>
     <row r="4">
@@ -2933,13 +2925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2947,14 +2939,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.9866666670000001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.978333333</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9812548695006634</v>
-      </c>
+        <v>0.993333333</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2963,13 +2951,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2977,13 +2965,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.606666667</v>
+        <v>0.413333333</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5883333335000001</v>
+        <v>0.404166667</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5845854986851003</v>
+        <v>0.3852428307822398</v>
       </c>
     </row>
     <row r="6">
@@ -2993,13 +2981,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3007,13 +2995,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.873333333</v>
+        <v>0.706666667</v>
       </c>
       <c r="G6" t="n">
-        <v>0.865</v>
+        <v>0.6933333335</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8647175506220238</v>
+        <v>0.6904483212093069</v>
       </c>
     </row>
     <row r="7">
@@ -3023,13 +3011,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3037,13 +3025,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.9866666670000001</v>
+        <v>0.766666667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.983333333</v>
+        <v>0.7466666665</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9844910926508779</v>
+        <v>0.7323201424258879</v>
       </c>
     </row>
     <row r="8">
@@ -3053,13 +3041,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3067,13 +3055,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.043333333</v>
+        <v>0.306666667</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03222222233333334</v>
+        <v>0.321666667</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0394019570750633</v>
+        <v>0.2918065384581127</v>
       </c>
     </row>
     <row r="9">
@@ -3083,13 +3071,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3097,13 +3085,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.86</v>
+        <v>0.796666667</v>
       </c>
       <c r="G9" t="n">
-        <v>0.865</v>
+        <v>0.8049999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8646702590253853</v>
+        <v>0.8095848206326297</v>
       </c>
     </row>
     <row r="10">
@@ -3133,7 +3121,7 @@
         <v>0.916666667</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9232311235112848</v>
+        <v>0.9209415779463459</v>
       </c>
     </row>
     <row r="11">
@@ -3143,13 +3131,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3157,13 +3145,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.046666667</v>
+        <v>0.24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03777777766666667</v>
+        <v>0.239166667</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04692389301361734</v>
+        <v>0.2133003104049293</v>
       </c>
     </row>
     <row r="12">
@@ -3173,13 +3161,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3187,13 +3175,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.786666667</v>
+        <v>0.826666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0.79</v>
+        <v>0.825</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7897072389569375</v>
+        <v>0.8221933065868315</v>
       </c>
     </row>
     <row r="13">
@@ -3203,13 +3191,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3217,13 +3205,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.956666667</v>
+        <v>0.643333333</v>
       </c>
       <c r="G13" t="n">
-        <v>0.96</v>
+        <v>0.6483333330000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9590703201198684</v>
+        <v>0.6481067739882954</v>
       </c>
     </row>
     <row r="14">
@@ -3233,13 +3221,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3247,13 +3235,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.496666667</v>
+        <v>0.83</v>
       </c>
       <c r="G14" t="n">
-        <v>0.494166667</v>
+        <v>0.8266666665</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5067848662662509</v>
+        <v>0.8290928268921984</v>
       </c>
     </row>
     <row r="15">
@@ -3263,13 +3251,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3277,13 +3265,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="G15" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7897162855129773</v>
+        <v>0.8577962504781058</v>
       </c>
     </row>
     <row r="16">
@@ -3293,13 +3281,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3307,13 +3295,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.903333333</v>
+        <v>0.316666667</v>
       </c>
       <c r="G16" t="n">
-        <v>0.916666667</v>
+        <v>0.2866666665</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9073534727821729</v>
+        <v>0.3063171783067324</v>
       </c>
     </row>
     <row r="17">
@@ -3323,13 +3311,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3337,13 +3325,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.45</v>
+        <v>0.863333333</v>
       </c>
       <c r="G17" t="n">
-        <v>0.421666667</v>
+        <v>0.875</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4425755471119286</v>
+        <v>0.8796085551288252</v>
       </c>
     </row>
     <row r="18">
@@ -3353,13 +3341,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3367,14 +3355,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.6966666665000001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.6971352237996813</v>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3383,13 +3367,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3397,10 +3381,14 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+        <v>1.44921875</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.444453125</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.500490083024639</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3409,13 +3397,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -3423,13 +3411,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.52203125</v>
+        <v>1.50375</v>
       </c>
       <c r="G20" t="n">
-        <v>1.52328125</v>
+        <v>1.502421875</v>
       </c>
       <c r="H20" t="n">
-        <v>1.52881116540268</v>
+        <v>1.507559562206124</v>
       </c>
     </row>
     <row r="21">
@@ -3439,13 +3427,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" t="n">
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -3453,14 +3441,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.589375</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.587265625</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.639883352191068</v>
-      </c>
+        <v>1.60703125</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3469,13 +3453,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" t="n">
         <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3483,13 +3467,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.682526433</v>
+        <v>1.385364496</v>
       </c>
       <c r="G22" t="n">
-        <v>1.541136485</v>
+        <v>1.24976475475</v>
       </c>
       <c r="H22" t="n">
-        <v>1.526106633804416</v>
+        <v>1.35509509604501</v>
       </c>
     </row>
     <row r="23">
@@ -3499,13 +3483,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C23" t="n">
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -3513,13 +3497,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.098219254</v>
+        <v>1.850862549</v>
       </c>
       <c r="G23" t="n">
-        <v>1.9634134615</v>
+        <v>1.705456731</v>
       </c>
       <c r="H23" t="n">
-        <v>1.950276557266211</v>
+        <v>1.677105190633442</v>
       </c>
     </row>
     <row r="24">
@@ -3529,13 +3513,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C24" t="n">
         <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3543,13 +3527,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.228992766</v>
+        <v>1.926265999</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1137720355</v>
+        <v>1.779115251</v>
       </c>
       <c r="H24" t="n">
-        <v>2.110728082995378</v>
+        <v>1.736190569335118</v>
       </c>
     </row>
     <row r="25">
@@ -3559,13 +3543,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C25" t="n">
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -3573,13 +3557,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>1.461111111</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>1.4101545095</v>
       </c>
       <c r="H25" t="n">
-        <v>1.000166597448705</v>
+        <v>1.579120377767806</v>
       </c>
     </row>
     <row r="26">
@@ -3589,13 +3573,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C26" t="n">
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3603,13 +3587,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.479059829</v>
+        <v>2.400854701</v>
       </c>
       <c r="G26" t="n">
-        <v>2.603993157</v>
+        <v>2.4809755625</v>
       </c>
       <c r="H26" t="n">
-        <v>2.605095785822404</v>
+        <v>2.490164811563365</v>
       </c>
     </row>
     <row r="27">
@@ -3639,7 +3623,7 @@
         <v>2.665299182</v>
       </c>
       <c r="H27" t="n">
-        <v>2.70328321661207</v>
+        <v>2.683950387448313</v>
       </c>
     </row>
     <row r="28">
@@ -3649,13 +3633,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C28" t="n">
         <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -3663,13 +3647,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>1.710181137</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>1.57054426425</v>
       </c>
       <c r="H28" t="n">
-        <v>1.000032268171346</v>
+        <v>1.7186627253567</v>
       </c>
     </row>
     <row r="29">
@@ -3679,13 +3663,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" t="n">
         <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -3693,13 +3677,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.026858214</v>
+        <v>3.090568395</v>
       </c>
       <c r="G29" t="n">
-        <v>2.954469053</v>
+        <v>3.0021691605</v>
       </c>
       <c r="H29" t="n">
-        <v>2.941021596806601</v>
+        <v>2.958901322971586</v>
       </c>
     </row>
     <row r="30">
@@ -3709,13 +3693,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D30" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -3723,13 +3707,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.286071205</v>
+        <v>3.179091688</v>
       </c>
       <c r="G30" t="n">
-        <v>3.2249950565</v>
+        <v>3.1771507205</v>
       </c>
       <c r="H30" t="n">
-        <v>3.160989401328982</v>
+        <v>3.249576222438726</v>
       </c>
     </row>
     <row r="31">
@@ -3739,13 +3723,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C31" t="n">
         <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3753,13 +3737,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.65638389</v>
+        <v>3.600685518</v>
       </c>
       <c r="G31" t="n">
-        <v>2.7074350505</v>
+        <v>3.730629434</v>
       </c>
       <c r="H31" t="n">
-        <v>2.845847470173482</v>
+        <v>3.757988770279086</v>
       </c>
     </row>
     <row r="32">
@@ -3769,13 +3753,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C32" t="n">
         <v>14</v>
       </c>
       <c r="D32" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3783,13 +3767,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.525278492</v>
+        <v>3.618680377</v>
       </c>
       <c r="G32" t="n">
-        <v>3.569837769</v>
+        <v>3.701668391</v>
       </c>
       <c r="H32" t="n">
-        <v>3.571395344744984</v>
+        <v>3.684440787655904</v>
       </c>
     </row>
     <row r="33">
@@ -3799,13 +3783,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3813,13 +3797,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.77377892</v>
+        <v>2.622767857</v>
       </c>
       <c r="G33" t="n">
-        <v>3.833954225</v>
+        <v>2.3504464285</v>
       </c>
       <c r="H33" t="n">
-        <v>3.84130538876534</v>
+        <v>2.437347758677244</v>
       </c>
     </row>
     <row r="34">
@@ -3829,13 +3813,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
         <v>16</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3843,13 +3827,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.094866071</v>
+        <v>4.3046875</v>
       </c>
       <c r="G34" t="n">
-        <v>2.95703125</v>
+        <v>4.353236606999999</v>
       </c>
       <c r="H34" t="n">
-        <v>3.136140177752402</v>
+        <v>4.291109528194886</v>
       </c>
     </row>
     <row r="35">
@@ -3859,13 +3843,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C35" t="n">
         <v>16</v>
       </c>
       <c r="D35" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -3873,14 +3857,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.943080357</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3.951450893</v>
-      </c>
-      <c r="H35" t="n">
-        <v>3.970632305330454</v>
-      </c>
+        <v>4.681919643</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3889,13 +3869,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C36" t="n">
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -3903,10 +3883,14 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+        <v>0.129812368</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.128152349</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.139127642848665</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3915,13 +3899,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C37" t="n">
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3929,13 +3913,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.155513347</v>
+        <v>0.149682126</v>
       </c>
       <c r="G37" t="n">
-        <v>0.15605445</v>
+        <v>0.147815524</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1591052722659665</v>
+        <v>0.1489808084363216</v>
       </c>
     </row>
     <row r="38">
@@ -3945,13 +3929,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" t="n">
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3959,14 +3943,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.180976271</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.179054038</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.1912647495083308</v>
-      </c>
+        <v>0.185595806</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3975,13 +3955,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" t="n">
         <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3989,13 +3969,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.12191595</v>
+        <v>0.056957217</v>
       </c>
       <c r="G39" t="n">
-        <v>0.089987731</v>
+        <v>0.023048103</v>
       </c>
       <c r="H39" t="n">
-        <v>0.09377808433928699</v>
+        <v>0.02842271369670921</v>
       </c>
     </row>
     <row r="40">
@@ -4005,13 +3985,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C40" t="n">
         <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -4019,13 +3999,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.226452432</v>
+        <v>0.160936952</v>
       </c>
       <c r="G40" t="n">
-        <v>0.193031172</v>
+        <v>0.127215326</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1983115114477628</v>
+        <v>0.1310669263790368</v>
       </c>
     </row>
     <row r="41">
@@ -4035,13 +4015,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C41" t="n">
         <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -4049,13 +4029,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.269507547</v>
+        <v>0.182634575</v>
       </c>
       <c r="G41" t="n">
-        <v>0.239327366</v>
+        <v>0.1467106635</v>
       </c>
       <c r="H41" t="n">
-        <v>0.244065947453406</v>
+        <v>0.1460038379678041</v>
       </c>
     </row>
     <row r="42">
@@ -4065,13 +4045,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C42" t="n">
         <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -4079,13 +4059,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.047106137</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.026351734</v>
       </c>
       <c r="H42" t="n">
-        <v>2.827230435570092e-05</v>
+        <v>0.03467287546618053</v>
       </c>
     </row>
     <row r="43">
@@ -4095,13 +4075,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
         <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -4109,13 +4089,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.249815332</v>
+        <v>0.226319718</v>
       </c>
       <c r="G43" t="n">
-        <v>0.256288826</v>
+        <v>0.231260654</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2595865022274733</v>
+        <v>0.2438466733937112</v>
       </c>
     </row>
     <row r="44">
@@ -4145,7 +4125,7 @@
         <v>0.2762237805</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2909977043278352</v>
+        <v>0.2908507757742949</v>
       </c>
     </row>
     <row r="45">
@@ -4155,13 +4135,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C45" t="n">
         <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -4169,13 +4149,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.049264635</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.029655365</v>
       </c>
       <c r="H45" t="n">
-        <v>1.935408004113694e-05</v>
+        <v>0.03676246650256158</v>
       </c>
     </row>
     <row r="46">
@@ -4185,13 +4165,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C46" t="n">
         <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -4199,13 +4179,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.260389238</v>
+        <v>0.276412389</v>
       </c>
       <c r="G46" t="n">
-        <v>0.252011052</v>
+        <v>0.2658732385</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2571933563219954</v>
+        <v>0.2651046697634868</v>
       </c>
     </row>
     <row r="47">
@@ -4215,13 +4195,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C47" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -4229,13 +4209,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.328983913</v>
+        <v>0.219689143</v>
       </c>
       <c r="G47" t="n">
-        <v>0.320763876</v>
+        <v>0.2181612135</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3261311194487929</v>
+        <v>0.2250336598548106</v>
       </c>
     </row>
     <row r="48">
@@ -4245,13 +4225,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C48" t="n">
         <v>14</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -4259,13 +4239,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.154289085</v>
+        <v>0.298662612</v>
       </c>
       <c r="G48" t="n">
-        <v>0.152936454</v>
+        <v>0.296335224</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1671687804816946</v>
+        <v>0.3040873382385305</v>
       </c>
     </row>
     <row r="49">
@@ -4275,13 +4255,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C49" t="n">
         <v>14</v>
       </c>
       <c r="D49" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -4289,13 +4269,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.281931145</v>
+        <v>0.306444136</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2791063565</v>
+        <v>0.3080103645</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2823823529675736</v>
+        <v>0.3069524839552783</v>
       </c>
     </row>
     <row r="50">
@@ -4305,13 +4285,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D50" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -4319,13 +4299,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.330783285</v>
+        <v>0.09732608700000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0.332519062</v>
+        <v>0.087212066</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3345948584515766</v>
+        <v>0.09058384229650809</v>
       </c>
     </row>
     <row r="51">
@@ -4335,13 +4315,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C51" t="n">
         <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -4349,13 +4329,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.151308161</v>
+        <v>0.329237345</v>
       </c>
       <c r="G51" t="n">
-        <v>0.139729186</v>
+        <v>0.334869079</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1517383480136813</v>
+        <v>0.3344353907129551</v>
       </c>
     </row>
     <row r="52">
@@ -4365,13 +4345,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C52" t="n">
         <v>16</v>
       </c>
       <c r="D52" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -4379,14 +4359,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.255832691</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.258613099</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.2598570600964515</v>
-      </c>
+        <v>0.367215621</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4474,7 +4450,7 @@
         <v>84</v>
       </c>
       <c r="C3" t="n">
-        <v>2.47060584704762</v>
+        <v>2.470605847047619</v>
       </c>
       <c r="D3" t="n">
         <v>0.961904333054255</v>
@@ -4502,7 +4478,7 @@
         <v>0.1966655542380952</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09910173622526636</v>
+        <v>0.09910173622526637</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -4570,7 +4546,7 @@
         <v>84</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4199440767716438</v>
+        <v>0.4199440767716437</v>
       </c>
       <c r="E2" t="n">
         <v>0.2599453112508386</v>
@@ -4591,7 +4567,7 @@
         <v>84</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8133941084268489</v>
+        <v>0.813394108426849</v>
       </c>
       <c r="E3" t="n">
         <v>0.6771825003618391</v>
@@ -4612,7 +4588,7 @@
         <v>84</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8285958471551902</v>
+        <v>0.8285958471551901</v>
       </c>
       <c r="E4" t="n">
         <v>0.8359852129437383</v>
@@ -4782,10 +4758,10 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7664285714999999</v>
+        <v>0.7664285715</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2660456366947869</v>
+        <v>0.266045636694787</v>
       </c>
       <c r="G5" t="n">
         <v>0.026666667</v>
@@ -4842,7 +4818,7 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1919475909999999</v>
+        <v>0.191947591</v>
       </c>
       <c r="F7" t="n">
         <v>0.08150604251050668</v>
@@ -4932,10 +4908,10 @@
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1988910847857142</v>
+        <v>0.1988910847857143</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09082536435386533</v>
+        <v>0.09082536435386532</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5025,7 +5001,7 @@
         <v>0.2192029269285714</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1020133523532524</v>
+        <v>0.1020133523532523</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -5052,7 +5028,7 @@
         <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6419047619285713</v>
+        <v>0.6419047619285714</v>
       </c>
       <c r="F14" t="n">
         <v>0.2809803177349913</v>
@@ -5142,7 +5118,7 @@
         <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6059523809285715</v>
+        <v>0.6059523809285714</v>
       </c>
       <c r="F17" t="n">
         <v>0.2877593324554842</v>
@@ -5202,7 +5178,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2223878863571429</v>
+        <v>0.2223878863571428</v>
       </c>
       <c r="F19" t="n">
         <v>0.1182158435893523</v>
@@ -5322,7 +5298,7 @@
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2877777778333333</v>
+        <v>0.2877777778333334</v>
       </c>
       <c r="F23" t="n">
         <v>0.1429633468244895</v>
@@ -5445,7 +5421,7 @@
         <v>1.965887044666667</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4810651135557213</v>
+        <v>0.4810651135557212</v>
       </c>
       <c r="G27" t="n">
         <v>1.2621875</v>
@@ -5535,7 +5511,7 @@
         <v>2.245144137166667</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6209598863471738</v>
+        <v>0.6209598863471739</v>
       </c>
       <c r="G30" t="n">
         <v>1.349375</v>
@@ -5652,7 +5628,7 @@
         <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1756434163333334</v>
+        <v>0.1756434163333333</v>
       </c>
       <c r="F34" t="n">
         <v>0.03049052598086902</v>
@@ -5772,7 +5748,7 @@
         <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7711111111666665</v>
+        <v>0.7711111111666668</v>
       </c>
       <c r="F38" t="n">
         <v>0.08683743860886356</v>
@@ -5952,7 +5928,7 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8416666666666667</v>
+        <v>0.8416666666666665</v>
       </c>
       <c r="F44" t="n">
         <v>0.0639704793930589</v>
@@ -6012,7 +5988,7 @@
         <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2469396333333333</v>
+        <v>0.2469396333333334</v>
       </c>
       <c r="F46" t="n">
         <v>0.04856220649984606</v>
@@ -6072,7 +6048,7 @@
         <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>2.874484841500001</v>
+        <v>2.8744848415</v>
       </c>
       <c r="F48" t="n">
         <v>1.016991221910414</v>
@@ -6312,10 +6288,10 @@
         <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9411111111666667</v>
+        <v>0.9411111111666668</v>
       </c>
       <c r="F56" t="n">
-        <v>0.03410224278928384</v>
+        <v>0.03410224278928383</v>
       </c>
       <c r="G56" t="n">
         <v>0.903333333</v>
@@ -6375,7 +6351,7 @@
         <v>0.2875145155</v>
       </c>
       <c r="F58" t="n">
-        <v>0.06117990189734384</v>
+        <v>0.06117990189734385</v>
       </c>
       <c r="G58" t="n">
         <v>0.180976271</v>
